--- a/data/dividends_info_20260507.xlsx
+++ b/data/dividends_info_20260507.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>48.78499984741211</v>
+        <v>48.25500106811523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1844829359055009</v>
+        <v>0.1865091659058485</v>
       </c>
       <c r="J2" t="n">
         <v>312</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>57.84999847412109</v>
+        <v>56.79999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.210025961043269</v>
+        <v>1.232394382750744</v>
       </c>
       <c r="J3" t="n">
         <v>291</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.619999885559082</v>
+        <v>9.640000343322754</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6237006311202571</v>
+        <v>0.6224066168375152</v>
       </c>
       <c r="J4" t="n">
         <v>221</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4779999852180481</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8620689903229801</v>
+        <v>0.8368201095603234</v>
       </c>
       <c r="J5" t="n">
         <v>221</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>48.78499984741211</v>
+        <v>48.25500106811523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1844829359055009</v>
+        <v>0.1865091659058485</v>
       </c>
       <c r="J6" t="n">
         <v>221</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.075000047683716</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I7" t="n">
-        <v>3.710843288218411</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J7" t="n">
         <v>200</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.940000057220459</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>3.367003334568775</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J8" t="n">
         <v>193</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.099999904632568</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9836065727547595</v>
+        <v>0.9917355059242088</v>
       </c>
       <c r="J9" t="n">
         <v>165</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4779999852180481</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8620689903229801</v>
+        <v>0.8368201095603234</v>
       </c>
       <c r="J10" t="n">
         <v>165</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.989999771118164</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7615230810218038</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J12" t="n">
         <v>144</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>48.78499984741211</v>
+        <v>48.25500106811523</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1844829359055009</v>
+        <v>0.1865091659058485</v>
       </c>
       <c r="J13" t="n">
         <v>137</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4779999852180481</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8620689903229801</v>
+        <v>0.8368201095603234</v>
       </c>
       <c r="J14" t="n">
         <v>109</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.989999771118164</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7615230810218038</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J15" t="n">
         <v>88</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.96999979019165</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="I16" t="n">
-        <v>4.187604837285504</v>
+        <v>4.244482269388714</v>
       </c>
       <c r="J16" t="n">
         <v>81</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9.694000244140625</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="I17" t="n">
-        <v>2.68207131681426</v>
+        <v>2.694300624641878</v>
       </c>
       <c r="J17" t="n">
         <v>74</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>15.80000019073486</v>
+        <v>15.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3.797468308588</v>
+        <v>3.870967741935484</v>
       </c>
       <c r="J18" t="n">
         <v>74</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.71399998664856</v>
+        <v>3.723999977111816</v>
       </c>
       <c r="I19" t="n">
-        <v>5.923532600723665</v>
+        <v>5.90762624468712</v>
       </c>
       <c r="J19" t="n">
         <v>74</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4779999852180481</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8620689903229801</v>
+        <v>0.8368201095603234</v>
       </c>
       <c r="J20" t="n">
         <v>74</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.28000020980835</v>
+        <v>6.164999961853027</v>
       </c>
       <c r="I21" t="n">
-        <v>3.821655923277815</v>
+        <v>3.892944063017685</v>
       </c>
       <c r="J21" t="n">
         <v>74</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>18.25</v>
+        <v>18.5</v>
       </c>
       <c r="I22" t="n">
-        <v>2.06027397260274</v>
+        <v>2.032432432432433</v>
       </c>
       <c r="J22" t="n">
         <v>74</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.96999979019165</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I23" t="n">
-        <v>2.010050321897042</v>
+        <v>2.047781523309159</v>
       </c>
       <c r="J23" t="n">
         <v>67</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3.970000028610229</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="I26" t="n">
-        <v>1.763224168653338</v>
+        <v>1.754385960719016</v>
       </c>
       <c r="J26" t="n">
         <v>60</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>36.45000076293945</v>
+        <v>37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.411522625131225</v>
+        <v>0.4054054054054054</v>
       </c>
       <c r="J27" t="n">
         <v>60</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.800000190734863</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6896551497342619</v>
+        <v>0.7079645898200416</v>
       </c>
       <c r="J28" t="n">
         <v>53</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>23.18000030517578</v>
+        <v>23.21999931335449</v>
       </c>
       <c r="I29" t="n">
-        <v>4.098360601780828</v>
+        <v>4.091300723913577</v>
       </c>
       <c r="J29" t="n">
         <v>46</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>27.54999923706055</v>
+        <v>27.20000076293945</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7078040123416192</v>
+        <v>0.7169117445970495</v>
       </c>
       <c r="J30" t="n">
         <v>46</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.960000038146973</v>
+        <v>1.904999971389771</v>
       </c>
       <c r="I31" t="n">
-        <v>1.683673436618855</v>
+        <v>1.732283490583217</v>
       </c>
       <c r="J31" t="n">
         <v>46</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.070000171661377</v>
+        <v>5.065000057220459</v>
       </c>
       <c r="I32" t="n">
-        <v>5.719920910869921</v>
+        <v>5.725567556244895</v>
       </c>
       <c r="J32" t="n">
         <v>46</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.595999956130981</v>
+        <v>2.589999914169312</v>
       </c>
       <c r="I34" t="n">
-        <v>5.338983141069319</v>
+        <v>5.351351528691191</v>
       </c>
       <c r="J34" t="n">
         <v>46</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>55.54999923706055</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="I35" t="n">
-        <v>1.134113426917369</v>
+        <v>1.147540951712049</v>
       </c>
       <c r="J35" t="n">
         <v>46</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.360000133514404</v>
+        <v>5.364999771118164</v>
       </c>
       <c r="I36" t="n">
-        <v>2.611940233445589</v>
+        <v>2.609506169108772</v>
       </c>
       <c r="J36" t="n">
         <v>46</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>19.64999961853027</v>
+        <v>19.85000038146973</v>
       </c>
       <c r="I37" t="n">
-        <v>3.969465725915064</v>
+        <v>3.929470957230519</v>
       </c>
       <c r="J37" t="n">
         <v>46</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>23.44000053405762</v>
+        <v>23.29999923706055</v>
       </c>
       <c r="I38" t="n">
-        <v>3.626279780859968</v>
+        <v>3.648068788980927</v>
       </c>
       <c r="J38" t="n">
         <v>46</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>48.77500152587891</v>
+        <v>48.25500106811523</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1845207528127868</v>
+        <v>0.1865091659058485</v>
       </c>
       <c r="J39" t="n">
         <v>46</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6.452000141143799</v>
+        <v>6.426000118255615</v>
       </c>
       <c r="I40" t="n">
-        <v>2.809981339644848</v>
+        <v>2.821350710606822</v>
       </c>
       <c r="J40" t="n">
         <v>46</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8.819999694824219</v>
+        <v>8.739999771118164</v>
       </c>
       <c r="I41" t="n">
-        <v>2.947845906985394</v>
+        <v>2.974828453190412</v>
       </c>
       <c r="J41" t="n">
         <v>46</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10.07499980926514</v>
+        <v>9.972000122070312</v>
       </c>
       <c r="I42" t="n">
-        <v>2.749379704655341</v>
+        <v>2.777777743774148</v>
       </c>
       <c r="J42" t="n">
         <v>46</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.174999952316284</v>
+        <v>1.195000052452087</v>
       </c>
       <c r="I43" t="n">
-        <v>1.148936216838764</v>
+        <v>1.129707063384524</v>
       </c>
       <c r="J43" t="n">
         <v>39</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.640000104904175</v>
+        <v>3.661999940872192</v>
       </c>
       <c r="I44" t="n">
-        <v>3.021977934885137</v>
+        <v>3.003823096015695</v>
       </c>
       <c r="J44" t="n">
         <v>39</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3.329999923706055</v>
+        <v>3.224999904632568</v>
       </c>
       <c r="I46" t="n">
-        <v>4.804804914888146</v>
+        <v>4.961240456787833</v>
       </c>
       <c r="J46" t="n">
         <v>32</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.9150000214576721</v>
+        <v>0.9049999713897705</v>
       </c>
       <c r="I47" t="n">
-        <v>2.73224037308468</v>
+        <v>2.762431026556669</v>
       </c>
       <c r="J47" t="n">
         <v>32</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>27.89999961853027</v>
+        <v>27.54999923706055</v>
       </c>
       <c r="I48" t="n">
-        <v>3.978494678052877</v>
+        <v>4.029038224098447</v>
       </c>
       <c r="J48" t="n">
         <v>28</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.5130000114440918</v>
+        <v>0.5139999985694885</v>
       </c>
       <c r="I50" t="n">
-        <v>4.483430699203134</v>
+        <v>4.47470818365977</v>
       </c>
       <c r="J50" t="n">
         <v>25</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>19.79999923706055</v>
+        <v>19.64999961853027</v>
       </c>
       <c r="I51" t="n">
-        <v>3.030303147067567</v>
+        <v>3.053435173780819</v>
       </c>
       <c r="J51" t="n">
         <v>25</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9.100000381469727</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="I52" t="n">
-        <v>2.197802105670883</v>
+        <v>2.202643190313694</v>
       </c>
       <c r="J52" t="n">
         <v>25</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2.559999942779541</v>
+        <v>2.565000057220459</v>
       </c>
       <c r="I53" t="n">
-        <v>7.031250157160687</v>
+        <v>7.017543703100556</v>
       </c>
       <c r="J53" t="n">
         <v>18</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>8.850000381469727</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I54" t="n">
-        <v>3.389830362359586</v>
+        <v>3.614457748264686</v>
       </c>
       <c r="J54" t="n">
         <v>18</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13.72000026702881</v>
+        <v>13.64000034332275</v>
       </c>
       <c r="I55" t="n">
-        <v>1.822157398938155</v>
+        <v>1.832844528646831</v>
       </c>
       <c r="J55" t="n">
         <v>18</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3.380000114440918</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8875739344453326</v>
+        <v>0.8746355514903141</v>
       </c>
       <c r="J56" t="n">
         <v>18</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>3.789999961853027</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="I57" t="n">
-        <v>3.957783680996692</v>
+        <v>3.947368470585578</v>
       </c>
       <c r="J57" t="n">
         <v>18</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.345999956130981</v>
+        <v>2.345000028610229</v>
       </c>
       <c r="I59" t="n">
-        <v>4.433077661753949</v>
+        <v>4.434967962948635</v>
       </c>
       <c r="J59" t="n">
         <v>11</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>11.11499977111816</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="I60" t="n">
-        <v>2.609086873339864</v>
+        <v>2.598566343773276</v>
       </c>
       <c r="J60" t="n">
         <v>11</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>2.075000047683716</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I61" t="n">
-        <v>3.710843288218411</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J61" t="n">
         <v>11</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>38.95999908447266</v>
+        <v>39</v>
       </c>
       <c r="I62" t="n">
-        <v>4.20944568413405</v>
+        <v>4.205128205128205</v>
       </c>
       <c r="J62" t="n">
         <v>11</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>37.59999847412109</v>
+        <v>35.66999816894531</v>
       </c>
       <c r="I63" t="n">
-        <v>5.319149152031316</v>
+        <v>5.606952909073097</v>
       </c>
       <c r="J63" t="n">
         <v>11</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>3.844000101089478</v>
+        <v>3.783999919891357</v>
       </c>
       <c r="I64" t="n">
-        <v>2.601456747403772</v>
+        <v>2.642706187025266</v>
       </c>
       <c r="J64" t="n">
         <v>11</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>31.3799991607666</v>
+        <v>31.6299991607666</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4731039004794326</v>
+        <v>0.4693645398010243</v>
       </c>
       <c r="J65" t="n">
         <v>11</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>23.60000038146973</v>
+        <v>23.21999931335449</v>
       </c>
       <c r="I66" t="n">
-        <v>3.898305021733671</v>
+        <v>3.962101753684728</v>
       </c>
       <c r="J66" t="n">
         <v>11</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>9.055000305175781</v>
+        <v>9.859999656677246</v>
       </c>
       <c r="I67" t="n">
-        <v>3.313086580775949</v>
+        <v>3.042596454826835</v>
       </c>
       <c r="J67" t="n">
         <v>11</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>85.81999969482422</v>
+        <v>85.45999908447266</v>
       </c>
       <c r="I68" t="n">
-        <v>1.211838736539546</v>
+        <v>1.216943612381759</v>
       </c>
       <c r="J68" t="n">
         <v>11</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>49.36999893188477</v>
+        <v>48.29999923706055</v>
       </c>
       <c r="I69" t="n">
-        <v>1.417865130938694</v>
+        <v>1.449275385211374</v>
       </c>
       <c r="J69" t="n">
         <v>11</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>57.84999847412109</v>
+        <v>56.79999923706055</v>
       </c>
       <c r="I70" t="n">
-        <v>3.802938734707416</v>
+        <v>3.873239488645198</v>
       </c>
       <c r="J70" t="n">
         <v>11</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>9.397000312805176</v>
+        <v>9.296999931335449</v>
       </c>
       <c r="I71" t="n">
-        <v>9.15185667098562</v>
+        <v>9.25029586266187</v>
       </c>
       <c r="J71" t="n">
         <v>11</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>12.81799983978271</v>
+        <v>12.70199966430664</v>
       </c>
       <c r="I72" t="n">
-        <v>4.368856350442059</v>
+        <v>4.408754643362435</v>
       </c>
       <c r="J72" t="n">
         <v>11</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>2.230000019073486</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I73" t="n">
-        <v>1.793721957752228</v>
+        <v>1.769911511893447</v>
       </c>
       <c r="J73" t="n">
         <v>11</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>87.59999847412109</v>
+        <v>85.30000305175781</v>
       </c>
       <c r="I76" t="n">
-        <v>2.351598214477787</v>
+        <v>2.415005775263626</v>
       </c>
       <c r="J76" t="n">
         <v>11</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>15.89000034332275</v>
+        <v>15.82999992370605</v>
       </c>
       <c r="I77" t="n">
-        <v>4.719949551890115</v>
+        <v>4.737839568001799</v>
       </c>
       <c r="J77" t="n">
         <v>11</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>16.03000068664551</v>
+        <v>15.59000015258789</v>
       </c>
       <c r="I78" t="n">
-        <v>1.871490874295022</v>
+        <v>1.924310436585858</v>
       </c>
       <c r="J78" t="n">
         <v>11</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>48.40000152587891</v>
+        <v>52.20000076293945</v>
       </c>
       <c r="I79" t="n">
-        <v>1.756198291740787</v>
+        <v>1.628352466621948</v>
       </c>
       <c r="J79" t="n">
         <v>11</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>35.91999816894531</v>
+        <v>35.58000183105469</v>
       </c>
       <c r="I80" t="n">
-        <v>2.366369831095561</v>
+        <v>2.388982451535764</v>
       </c>
       <c r="J80" t="n">
         <v>11</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>62.97999954223633</v>
+        <v>64.23999786376953</v>
       </c>
       <c r="I81" t="n">
-        <v>2.064147363367604</v>
+        <v>2.023661337531242</v>
       </c>
       <c r="J81" t="n">
         <v>11</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>8.140000343322754</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I82" t="n">
-        <v>7.371007060118619</v>
+        <v>7.407407058555364</v>
       </c>
       <c r="J82" t="n">
         <v>11</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>6.25</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I83" t="n">
-        <v>7.519999999999999</v>
+        <v>7.580645394498929</v>
       </c>
       <c r="J83" t="n">
         <v>11</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>5.940000057220459</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I84" t="n">
-        <v>3.367003334568775</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J84" t="n">
         <v>11</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>22.84000015258789</v>
+        <v>22.81999969482422</v>
       </c>
       <c r="I85" t="n">
-        <v>4.378283683534455</v>
+        <v>4.382121005140982</v>
       </c>
       <c r="J85" t="n">
         <v>11</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4.840000152587891</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="I86" t="n">
-        <v>4.442148620285518</v>
+        <v>4.469854523028509</v>
       </c>
       <c r="J86" t="n">
         <v>11</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>22.55500030517578</v>
+        <v>22.38500022888184</v>
       </c>
       <c r="I87" t="n">
-        <v>1.197073803355445</v>
+        <v>1.206164830195702</v>
       </c>
       <c r="J87" t="n">
         <v>11</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>8.399999618530273</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="I88" t="n">
-        <v>2.380952489078726</v>
+        <v>2.450980437988963</v>
       </c>
       <c r="J88" t="n">
         <v>11</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>9.385000228881836</v>
+        <v>9.345000267028809</v>
       </c>
       <c r="I89" t="n">
-        <v>2.557272180573985</v>
+        <v>2.568218225169796</v>
       </c>
       <c r="J89" t="n">
         <v>11</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>21.57999992370605</v>
+        <v>21.51000022888184</v>
       </c>
       <c r="I90" t="n">
-        <v>3.660797047233395</v>
+        <v>3.672710328190763</v>
       </c>
       <c r="J90" t="n">
         <v>11</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>5.199999809265137</v>
+        <v>5.21999979019165</v>
       </c>
       <c r="I91" t="n">
-        <v>1.788461604061919</v>
+        <v>1.781609267010824</v>
       </c>
       <c r="J91" t="n">
         <v>11</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>6.099999904632568</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9836065727547595</v>
+        <v>0.9917355059242088</v>
       </c>
       <c r="J92" t="n">
         <v>11</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>36.72000122070312</v>
+        <v>36.11999893188477</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9531590097079471</v>
+        <v>0.9689922767163736</v>
       </c>
       <c r="J93" t="n">
         <v>11</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>7.184999942779541</v>
+        <v>7.264999866485596</v>
       </c>
       <c r="I94" t="n">
-        <v>7.714683429566838</v>
+        <v>7.629731730031533</v>
       </c>
       <c r="J94" t="n">
         <v>11</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>2.279999971389771</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I95" t="n">
-        <v>2.631578980390385</v>
+        <v>2.620087379890132</v>
       </c>
       <c r="J95" t="n">
         <v>11</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>12.80000019073486</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="I96" t="n">
-        <v>1.562499976716936</v>
+        <v>1.550387642746198</v>
       </c>
       <c r="J96" t="n">
         <v>11</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>7.630000114440918</v>
+        <v>7.815000057220459</v>
       </c>
       <c r="I97" t="n">
-        <v>1.349934448953114</v>
+        <v>1.3179782373109</v>
       </c>
       <c r="J97" t="n">
         <v>11</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5.979000091552734</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="I98" t="n">
-        <v>3.177788879254848</v>
+        <v>3.204047310288562</v>
       </c>
       <c r="J98" t="n">
         <v>11</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>10.3149995803833</v>
+        <v>10.35999965667725</v>
       </c>
       <c r="I99" t="n">
-        <v>4.18807578840393</v>
+        <v>4.169884308071058</v>
       </c>
       <c r="J99" t="n">
         <v>11</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>27.92000007629395</v>
+        <v>27.68000030517578</v>
       </c>
       <c r="I100" t="n">
-        <v>1.575931227785315</v>
+        <v>1.589595358197037</v>
       </c>
       <c r="J100" t="n">
         <v>11</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>8.470000267028809</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I102" t="n">
-        <v>5.548996283147359</v>
+        <v>5.595238349335005</v>
       </c>
       <c r="J102" t="n">
         <v>11</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>55.06000137329102</v>
+        <v>54.86000061035156</v>
       </c>
       <c r="I103" t="n">
-        <v>2.542680648531774</v>
+        <v>2.551950390856965</v>
       </c>
       <c r="J103" t="n">
         <v>11</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>4.201000213623047</v>
+        <v>4.181000232696533</v>
       </c>
       <c r="I104" t="n">
-        <v>7.141156504280978</v>
+        <v>7.175316510482832</v>
       </c>
       <c r="J104" t="n">
         <v>11</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>12.69999980926514</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9448819039544819</v>
+        <v>0.9302325856477186</v>
       </c>
       <c r="J105" t="n">
         <v>11</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>3.559999942779541</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="I106" t="n">
-        <v>4.775280975630273</v>
+        <v>4.802259938754712</v>
       </c>
       <c r="J106" t="n">
         <v>11</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>21.70000076293945</v>
+        <v>21.60000038146973</v>
       </c>
       <c r="I107" t="n">
-        <v>3.225806338198391</v>
+        <v>3.2407406835072</v>
       </c>
       <c r="J107" t="n">
         <v>11</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>2.440000057220459</v>
+        <v>2.420000076293945</v>
       </c>
       <c r="I108" t="n">
-        <v>1.434426195869457</v>
+        <v>1.446280946139471</v>
       </c>
       <c r="J108" t="n">
         <v>11</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>6.150000095367432</v>
+        <v>6.130000114440918</v>
       </c>
       <c r="I109" t="n">
-        <v>5.365853575328834</v>
+        <v>5.383360421520929</v>
       </c>
       <c r="J109" t="n">
         <v>11</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9729999899864197</v>
+        <v>0.9700000286102295</v>
       </c>
       <c r="I110" t="n">
-        <v>7.194244678355753</v>
+        <v>7.216494632509725</v>
       </c>
       <c r="J110" t="n">
         <v>11</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>49.72000122070312</v>
+        <v>49.79999923706055</v>
       </c>
       <c r="I111" t="n">
-        <v>1.427996746919548</v>
+        <v>1.425702833086846</v>
       </c>
       <c r="J111" t="n">
         <v>11</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>98.84999847412109</v>
+        <v>98.59999847412109</v>
       </c>
       <c r="I112" t="n">
-        <v>1.365705635648978</v>
+        <v>1.369168378186462</v>
       </c>
       <c r="J112" t="n">
         <v>11</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>7.139999866485596</v>
+        <v>7.019999980926514</v>
       </c>
       <c r="I113" t="n">
-        <v>1.120448200223526</v>
+        <v>1.13960114269746</v>
       </c>
       <c r="J113" t="n">
         <v>11</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>1.239669421487603</v>
       </c>
       <c r="J114" t="n">
         <v>11</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>4.420000076293945</v>
+        <v>4.334000110626221</v>
       </c>
       <c r="I115" t="n">
-        <v>3.846153779765103</v>
+        <v>3.922473365498754</v>
       </c>
       <c r="J115" t="n">
         <v>11</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>57</v>
+        <v>56.70000076293945</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7936507829716493</v>
       </c>
       <c r="J117" t="n">
         <v>11</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>5.139999866485596</v>
+        <v>5.039999961853027</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7782101369459655</v>
+        <v>0.7936507996578126</v>
       </c>
       <c r="J118" t="n">
         <v>11</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>34.20000076293945</v>
+        <v>34.02000045776367</v>
       </c>
       <c r="I119" t="n">
-        <v>3.070175370106494</v>
+        <v>3.086419711556414</v>
       </c>
       <c r="J119" t="n">
         <v>11</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>21.34000015258789</v>
+        <v>21.04000091552734</v>
       </c>
       <c r="I121" t="n">
-        <v>1.780693520538319</v>
+        <v>1.806083571600813</v>
       </c>
       <c r="J121" t="n">
         <v>11</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>24.89999961853027</v>
+        <v>24.75</v>
       </c>
       <c r="I122" t="n">
-        <v>2.409638591132698</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="J122" t="n">
         <v>11</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>34.45000076293945</v>
+        <v>34.04999923706055</v>
       </c>
       <c r="I123" t="n">
-        <v>1.015965144408711</v>
+        <v>1.027900169874467</v>
       </c>
       <c r="J123" t="n">
         <v>11</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2.904999971389771</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3442340825640675</v>
+        <v>0.3496503624754485</v>
       </c>
       <c r="J125" t="n">
         <v>11</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>22.20999908447266</v>
+        <v>22.27000045776367</v>
       </c>
       <c r="I126" t="n">
-        <v>5.042773733309196</v>
+        <v>5.029187144042247</v>
       </c>
       <c r="J126" t="n">
         <v>11</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1.620000004768372</v>
+        <v>1.649999976158142</v>
       </c>
       <c r="I127" t="n">
-        <v>6.172839488003462</v>
+        <v>6.060606148179462</v>
       </c>
       <c r="J127" t="n">
         <v>11</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>8.739999771118164</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="I128" t="n">
-        <v>2.974828453190412</v>
+        <v>2.988505812645086</v>
       </c>
       <c r="J128" t="n">
         <v>11</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2.101999998092651</v>
+        <v>2.109999895095825</v>
       </c>
       <c r="I129" t="n">
-        <v>4.391056140996801</v>
+        <v>4.374407800423525</v>
       </c>
       <c r="J129" t="n">
         <v>11</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>9.319999694824219</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I130" t="n">
-        <v>3.755364929833307</v>
+        <v>3.723404406421921</v>
       </c>
       <c r="J130" t="n">
         <v>4</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>5.199999809265137</v>
+        <v>5.25</v>
       </c>
       <c r="I131" t="n">
-        <v>1.846153913870368</v>
+        <v>1.828571428571429</v>
       </c>
       <c r="J131" t="n">
         <v>4</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>12</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="I133" t="n">
-        <v>1.666666666666667</v>
+        <v>1.652892509873682</v>
       </c>
       <c r="J133" t="n">
         <v>4</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.619999885559082</v>
+        <v>9.640000343322754</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6237006311202571</v>
+        <v>0.6224066168375152</v>
       </c>
       <c r="J134" t="n">
         <v>4</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>19.8799991607666</v>
+        <v>19.95999908447266</v>
       </c>
       <c r="I135" t="n">
-        <v>2.515090649434008</v>
+        <v>2.505010134940144</v>
       </c>
       <c r="J135" t="n">
         <v>4</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>16.95999908447266</v>
+        <v>16.68000030517578</v>
       </c>
       <c r="I137" t="n">
-        <v>2.948113366690943</v>
+        <v>2.997601863621373</v>
       </c>
       <c r="J137" t="n">
         <v>4</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>4.300000190734863</v>
+        <v>4.320000171661377</v>
       </c>
       <c r="I138" t="n">
-        <v>2.325581292193156</v>
+        <v>2.314814722832342</v>
       </c>
       <c r="J138" t="n">
         <v>4</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>3.599999904632568</v>
+        <v>3.630000114440918</v>
       </c>
       <c r="I139" t="n">
-        <v>3.055555636500137</v>
+        <v>3.030302934768416</v>
       </c>
       <c r="J139" t="n">
         <v>4</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>9.199999809265137</v>
+        <v>8.949999809265137</v>
       </c>
       <c r="I140" t="n">
-        <v>0.923913062632873</v>
+        <v>0.9497206906307091</v>
       </c>
       <c r="J140" t="n">
         <v>4</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>4.889999866485596</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I141" t="n">
-        <v>1.942740339342294</v>
+        <v>1.919191993142792</v>
       </c>
       <c r="J141" t="n">
         <v>4</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1.200000047683716</v>
+        <v>1.240000009536743</v>
       </c>
       <c r="I142" t="n">
-        <v>2.49999990065893</v>
+        <v>2.419354820102608</v>
       </c>
       <c r="J142" t="n">
         <v>4</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>7.269999980926514</v>
+        <v>7.260000228881836</v>
       </c>
       <c r="I145" t="n">
-        <v>3.026134808489538</v>
+        <v>3.030302934768416</v>
       </c>
       <c r="J145" t="n">
         <v>4</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>26.04999923706055</v>
+        <v>26.25</v>
       </c>
       <c r="I146" t="n">
-        <v>2.341650740366132</v>
+        <v>2.323809523809524</v>
       </c>
       <c r="J146" t="n">
         <v>-3</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>3</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="I147" t="n">
-        <v>5</v>
+        <v>4.950495096249109</v>
       </c>
       <c r="J147" t="n">
         <v>-3</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>11.60000038146973</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="I148" t="n">
-        <v>6.034482560174792</v>
+        <v>6.167400673772982</v>
       </c>
       <c r="J148" t="n">
         <v>-3</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>8.75</v>
+        <v>8.760000228881836</v>
       </c>
       <c r="I149" t="n">
-        <v>5.834285714285715</v>
+        <v>5.827625418511689</v>
       </c>
       <c r="J149" t="n">
         <v>-3</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>8.024999618530273</v>
+        <v>8.375</v>
       </c>
       <c r="I150" t="n">
-        <v>3.364486141239827</v>
+        <v>3.223880597014925</v>
       </c>
       <c r="J150" t="n">
         <v>-3</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>5.864999771118164</v>
+        <v>5.885000228881836</v>
       </c>
       <c r="I151" t="n">
-        <v>5.967604665963566</v>
+        <v>5.947323473027303</v>
       </c>
       <c r="J151" t="n">
         <v>-3</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>18</v>
+        <v>17.95000076293945</v>
       </c>
       <c r="I153" t="n">
-        <v>4.166666666666666</v>
+        <v>4.178272802909796</v>
       </c>
       <c r="J153" t="n">
         <v>-3</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>4.210000038146973</v>
+        <v>4.224999904632568</v>
       </c>
       <c r="I155" t="n">
-        <v>3.562945335887036</v>
+        <v>3.55029593812606</v>
       </c>
       <c r="J155" t="n">
         <v>-3</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.14000034332275</v>
+        <v>11.84000015258789</v>
       </c>
       <c r="I156" t="n">
-        <v>1.624126807446484</v>
+        <v>1.665278694754952</v>
       </c>
       <c r="J156" t="n">
         <v>-3</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>28.85000038146973</v>
+        <v>28.5</v>
       </c>
       <c r="I157" t="n">
-        <v>3.812824906257287</v>
+        <v>3.859649122807018</v>
       </c>
       <c r="J157" t="n">
         <v>-3</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>59.29999923706055</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7925801113775823</v>
+        <v>0.7859531872848611</v>
       </c>
       <c r="J158" t="n">
         <v>-3</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>77.09999847412109</v>
+        <v>77.5</v>
       </c>
       <c r="I159" t="n">
-        <v>1.556420264266003</v>
+        <v>1.548387096774194</v>
       </c>
       <c r="J159" t="n">
         <v>-3</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>25.54999923706055</v>
+        <v>25.75</v>
       </c>
       <c r="I160" t="n">
-        <v>1.056751499265652</v>
+        <v>1.048543689320389</v>
       </c>
       <c r="J160" t="n">
         <v>-3</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>28.64999961853027</v>
+        <v>29.35000038146973</v>
       </c>
       <c r="I162" t="n">
-        <v>1.047120432790392</v>
+        <v>1.02214649438099</v>
       </c>
       <c r="J162" t="n">
         <v>-3</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>0.1861999928951263</v>
+        <v>0.1829999983310699</v>
       </c>
       <c r="I163" t="n">
-        <v>3.759398639688788</v>
+        <v>3.825136646906478</v>
       </c>
       <c r="J163" t="n">
         <v>-10</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>6.900000095367432</v>
+        <v>6.920000076293945</v>
       </c>
       <c r="I164" t="n">
-        <v>2.318840547660599</v>
+        <v>2.312138702832054</v>
       </c>
       <c r="J164" t="n">
         <v>-10</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>2.164999961853027</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="I165" t="n">
-        <v>3.002309521722411</v>
+        <v>3.023255679851103</v>
       </c>
       <c r="J165" t="n">
         <v>-10</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>7.650000095367432</v>
+        <v>7.53000020980835</v>
       </c>
       <c r="I166" t="n">
-        <v>3.267973815469507</v>
+        <v>3.320053028343314</v>
       </c>
       <c r="J166" t="n">
         <v>-10</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>1.370000004768372</v>
+        <v>1.299999952316284</v>
       </c>
       <c r="I167" t="n">
-        <v>5.109489033310991</v>
+        <v>5.384615582121908</v>
       </c>
       <c r="J167" t="n">
         <v>-10</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>7.159999847412109</v>
+        <v>7.230000019073486</v>
       </c>
       <c r="I168" t="n">
-        <v>6.983240372284626</v>
+        <v>6.915629304024182</v>
       </c>
       <c r="J168" t="n">
         <v>-17</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>19.54999923706055</v>
+        <v>19.2450008392334</v>
       </c>
       <c r="I169" t="n">
-        <v>3.324808313893986</v>
+        <v>3.377500502233763</v>
       </c>
       <c r="J169" t="n">
         <v>-17</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>12.88500022888184</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="I170" t="n">
-        <v>4.19091959959446</v>
+        <v>4.218749937135727</v>
       </c>
       <c r="J170" t="n">
         <v>-17</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>5.763999938964844</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="I171" t="n">
-        <v>1.734906333429958</v>
+        <v>1.785714316124819</v>
       </c>
       <c r="J171" t="n">
         <v>-17</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>9.579999923706055</v>
+        <v>8.539999961853027</v>
       </c>
       <c r="I172" t="n">
-        <v>1.670146151087895</v>
+        <v>1.87353630813463</v>
       </c>
       <c r="J172" t="n">
         <v>-17</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>287.25</v>
+        <v>288.8500061035156</v>
       </c>
       <c r="I173" t="n">
-        <v>1.258485639686684</v>
+        <v>1.251514600524013</v>
       </c>
       <c r="J173" t="n">
         <v>-17</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>30.20000076293945</v>
+        <v>30.39999961853027</v>
       </c>
       <c r="I174" t="n">
-        <v>4.503311144511466</v>
+        <v>4.473684266663655</v>
       </c>
       <c r="J174" t="n">
         <v>-17</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>13.95499992370605</v>
+        <v>13.90999984741211</v>
       </c>
       <c r="I175" t="n">
-        <v>41.71694755877826</v>
+        <v>41.85190556334249</v>
       </c>
       <c r="J175" t="n">
         <v>-17</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>16.48999977111816</v>
+        <v>15.59000015258789</v>
       </c>
       <c r="I176" t="n">
-        <v>3.54760465809474</v>
+        <v>3.752405351342424</v>
       </c>
       <c r="J176" t="n">
         <v>-17</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>20.57999992370605</v>
+        <v>20.35000038146973</v>
       </c>
       <c r="I177" t="n">
-        <v>3.061224501144456</v>
+        <v>3.095823037790527</v>
       </c>
       <c r="J177" t="n">
         <v>-17</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>145.4499969482422</v>
+        <v>143.6499938964844</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6187693495244703</v>
+        <v>0.6265228250887007</v>
       </c>
       <c r="J178" t="n">
         <v>-17</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>71.62999725341797</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="I179" t="n">
-        <v>2.402345478127027</v>
+        <v>2.410083982107895</v>
       </c>
       <c r="J179" t="n">
         <v>-17</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>27</v>
+        <v>26.70000076293945</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5185185185185186</v>
+        <v>0.5243445543055001</v>
       </c>
       <c r="J180" t="n">
         <v>-24</v>
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>1.519999980926514</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="I181" t="n">
-        <v>3.947368470585578</v>
+        <v>4.026845611810072</v>
       </c>
       <c r="J181" t="n">
         <v>-24</v>
@@ -8959,7 +8959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C288"/>
+  <dimension ref="A1:C298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10546,7 +10546,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10556,14 +10556,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10580,7 +10580,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10624,14 +10624,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10648,7 +10648,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10665,7 +10665,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10818,7 +10818,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10896,14 +10896,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10920,7 +10920,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10937,7 +10937,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10954,7 +10954,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10964,14 +10964,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10981,14 +10981,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10998,14 +10998,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11015,14 +11015,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11032,14 +11032,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11049,14 +11049,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11066,14 +11066,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11090,7 +11090,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11100,14 +11100,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11117,14 +11117,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11141,7 +11141,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11151,14 +11151,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11175,7 +11175,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11185,14 +11185,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11202,14 +11202,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11226,7 +11226,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11243,7 +11243,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11253,14 +11253,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11277,7 +11277,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11294,7 +11294,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11311,7 +11311,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11328,7 +11328,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11338,14 +11338,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11355,14 +11355,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11379,7 +11379,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11396,7 +11396,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11413,7 +11413,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11430,7 +11430,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11440,14 +11440,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11457,14 +11457,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11474,14 +11474,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11491,14 +11491,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11515,7 +11515,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11532,7 +11532,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11542,14 +11542,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11566,7 +11566,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11583,7 +11583,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11600,7 +11600,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11610,14 +11610,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11651,7 +11651,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11661,14 +11661,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11678,14 +11678,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11702,7 +11702,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11712,14 +11712,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11729,14 +11729,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11753,7 +11753,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11770,7 +11770,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11780,14 +11780,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11797,14 +11797,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11821,7 +11821,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11838,7 +11838,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11855,7 +11855,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11872,7 +11872,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11882,36 +11882,36 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11923,29 +11923,29 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11957,29 +11957,29 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11991,12 +11991,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -12008,12 +12008,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -12025,29 +12025,29 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12059,7 +12059,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12069,14 +12069,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12086,14 +12086,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12103,14 +12103,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12120,14 +12120,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12144,7 +12144,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12161,7 +12161,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12171,14 +12171,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12188,14 +12188,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12212,7 +12212,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12222,14 +12222,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12246,7 +12246,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12263,7 +12263,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12273,14 +12273,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12290,36 +12290,36 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12331,63 +12331,63 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12399,97 +12399,97 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12501,114 +12501,114 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12620,12 +12620,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12637,12 +12637,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -12654,41 +12654,41 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12705,7 +12705,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12722,7 +12722,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12732,41 +12732,41 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -12790,12 +12790,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -12807,46 +12807,46 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -12858,29 +12858,29 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -12892,12 +12892,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -12909,63 +12909,63 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -12977,29 +12977,29 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -13011,80 +13011,80 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -13096,12 +13096,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -13113,63 +13113,63 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -13181,12 +13181,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -13198,46 +13198,46 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -13249,12 +13249,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -13266,12 +13266,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -13283,29 +13283,29 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -13317,29 +13317,29 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -13351,24 +13351,24 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13385,7 +13385,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13402,7 +13402,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13419,7 +13419,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13436,80 +13436,80 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -13521,12 +13521,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -13538,75 +13538,75 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13623,7 +13623,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13657,7 +13657,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13674,7 +13674,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13684,14 +13684,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13708,12 +13708,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -13725,12 +13725,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -13742,80 +13742,80 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -13827,12 +13827,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -13844,15 +13844,185 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
+          <t>CULTI Milano S.p.A.</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Cloudia Research S.p.A.</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>TMP Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>ACEA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>ASCOPIAVE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ACEA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ASCOPIAVE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
           <t>B.F. S.p.A.</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>OLIDATA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -13882,112 +14052,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EXPERT.AI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OMER S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>